--- a/artfynd/S 222-2023 artfynd.xlsx
+++ b/artfynd/S 222-2023 artfynd.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Julia Odéhn, Elin Jonsson</t>
+          <t>Elin Jonsson, Julia Odéhn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -993,7 +993,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Frida Gustafsson, Elin Jonsson</t>
+          <t>Elin Jonsson, Frida Gustafsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Frida Gustafsson, Elin Jonsson</t>
+          <t>Elin Jonsson, Frida Gustafsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Julia Odéhn, Elin Jonsson</t>
+          <t>Elin Jonsson, Julia Odéhn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Frida Gustafsson, Elin Jonsson</t>
+          <t>Elin Jonsson, Frida Gustafsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sofia Asplund, Elin Jonsson</t>
+          <t>Elin Jonsson, Sofia Asplund</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sofia Asplund, Elin Jonsson</t>
+          <t>Elin Jonsson, Sofia Asplund</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/S 222-2023 artfynd.xlsx
+++ b/artfynd/S 222-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136274561</v>
       </c>
       <c r="B3" t="n">
-        <v>96645</v>
+        <v>96648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136274569</v>
       </c>
       <c r="B4" t="n">
-        <v>96645</v>
+        <v>96648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136274571</v>
       </c>
       <c r="B5" t="n">
-        <v>96554</v>
+        <v>96557</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136274587</v>
       </c>
       <c r="B6" t="n">
-        <v>96554</v>
+        <v>96557</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136274562</v>
       </c>
       <c r="B7" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136274573</v>
       </c>
       <c r="B8" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136274586</v>
       </c>
       <c r="B9" t="n">
-        <v>99148</v>
+        <v>99151</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>136274678</v>
       </c>
       <c r="B20" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136274680</v>
       </c>
       <c r="B21" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>136274674</v>
       </c>
       <c r="B24" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>136274683</v>
       </c>
       <c r="B25" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136274684</v>
       </c>
       <c r="B26" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>136274766</v>
       </c>
       <c r="B27" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>136274632</v>
       </c>
       <c r="B28" t="n">
-        <v>96450</v>
+        <v>96453</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>136274598</v>
       </c>
       <c r="B46" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>136274628</v>
       </c>
       <c r="B47" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>136274668</v>
       </c>
       <c r="B48" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>136274606</v>
       </c>
       <c r="B49" t="n">
-        <v>98207</v>
+        <v>98210</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>136274590</v>
       </c>
       <c r="B50" t="n">
-        <v>102790</v>
+        <v>102793</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>136274592</v>
       </c>
       <c r="B51" t="n">
-        <v>102790</v>
+        <v>102793</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>136274621</v>
       </c>
       <c r="B52" t="n">
-        <v>102790</v>
+        <v>102793</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>136274633</v>
       </c>
       <c r="B53" t="n">
-        <v>102790</v>
+        <v>102793</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>136274638</v>
       </c>
       <c r="B54" t="n">
-        <v>102790</v>
+        <v>102793</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136274647</v>
       </c>
       <c r="B55" t="n">
-        <v>102790</v>
+        <v>102793</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136274664</v>
       </c>
       <c r="B56" t="n">
-        <v>102790</v>
+        <v>102793</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>136274667</v>
       </c>
       <c r="B57" t="n">
-        <v>102790</v>
+        <v>102793</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>136274670</v>
       </c>
       <c r="B58" t="n">
-        <v>102790</v>
+        <v>102793</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>136274565</v>
       </c>
       <c r="B59" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136274597</v>
       </c>
       <c r="B60" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/S 222-2023 artfynd.xlsx
+++ b/artfynd/S 222-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136274561</v>
       </c>
       <c r="B3" t="n">
-        <v>96648</v>
+        <v>96649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136274569</v>
       </c>
       <c r="B4" t="n">
-        <v>96648</v>
+        <v>96649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136274571</v>
       </c>
       <c r="B5" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136274587</v>
       </c>
       <c r="B6" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136274562</v>
       </c>
       <c r="B7" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136274573</v>
       </c>
       <c r="B8" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136274586</v>
       </c>
       <c r="B9" t="n">
-        <v>99151</v>
+        <v>99152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>136274678</v>
       </c>
       <c r="B20" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136274680</v>
       </c>
       <c r="B21" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>136274674</v>
       </c>
       <c r="B24" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>136274683</v>
       </c>
       <c r="B25" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136274684</v>
       </c>
       <c r="B26" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>136274766</v>
       </c>
       <c r="B27" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>136274632</v>
       </c>
       <c r="B28" t="n">
-        <v>96453</v>
+        <v>96454</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>136274598</v>
       </c>
       <c r="B46" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>136274628</v>
       </c>
       <c r="B47" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>136274668</v>
       </c>
       <c r="B48" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>136274606</v>
       </c>
       <c r="B49" t="n">
-        <v>98210</v>
+        <v>98211</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>136274590</v>
       </c>
       <c r="B50" t="n">
-        <v>102793</v>
+        <v>102794</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>136274592</v>
       </c>
       <c r="B51" t="n">
-        <v>102793</v>
+        <v>102794</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>136274621</v>
       </c>
       <c r="B52" t="n">
-        <v>102793</v>
+        <v>102794</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>136274633</v>
       </c>
       <c r="B53" t="n">
-        <v>102793</v>
+        <v>102794</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>136274638</v>
       </c>
       <c r="B54" t="n">
-        <v>102793</v>
+        <v>102794</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136274647</v>
       </c>
       <c r="B55" t="n">
-        <v>102793</v>
+        <v>102794</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136274664</v>
       </c>
       <c r="B56" t="n">
-        <v>102793</v>
+        <v>102794</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>136274667</v>
       </c>
       <c r="B57" t="n">
-        <v>102793</v>
+        <v>102794</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>136274670</v>
       </c>
       <c r="B58" t="n">
-        <v>102793</v>
+        <v>102794</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>136274565</v>
       </c>
       <c r="B59" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136274597</v>
       </c>
       <c r="B60" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/S 222-2023 artfynd.xlsx
+++ b/artfynd/S 222-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136274561</v>
       </c>
       <c r="B3" t="n">
-        <v>96649</v>
+        <v>96654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136274569</v>
       </c>
       <c r="B4" t="n">
-        <v>96649</v>
+        <v>96654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136274571</v>
       </c>
       <c r="B5" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136274587</v>
       </c>
       <c r="B6" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136274562</v>
       </c>
       <c r="B7" t="n">
-        <v>102472</v>
+        <v>102477</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136274573</v>
       </c>
       <c r="B8" t="n">
-        <v>102472</v>
+        <v>102477</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136274586</v>
       </c>
       <c r="B9" t="n">
-        <v>99152</v>
+        <v>99157</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>136274678</v>
       </c>
       <c r="B20" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136274680</v>
       </c>
       <c r="B21" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>136274673</v>
       </c>
       <c r="B22" t="n">
-        <v>56946</v>
+        <v>56948</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>136274681</v>
       </c>
       <c r="B23" t="n">
-        <v>43409</v>
+        <v>43411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>136274674</v>
       </c>
       <c r="B24" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>136274683</v>
       </c>
       <c r="B25" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136274684</v>
       </c>
       <c r="B26" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>136274766</v>
       </c>
       <c r="B27" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>136274632</v>
       </c>
       <c r="B28" t="n">
-        <v>96454</v>
+        <v>96459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136274579</v>
       </c>
       <c r="B29" t="n">
-        <v>75564</v>
+        <v>75566</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136274660</v>
       </c>
       <c r="B30" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>136274567</v>
       </c>
       <c r="B31" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136274570</v>
       </c>
       <c r="B32" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>136274575</v>
       </c>
       <c r="B33" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>136274589</v>
       </c>
       <c r="B34" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>136274596</v>
       </c>
       <c r="B35" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>136274600</v>
       </c>
       <c r="B36" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>136274601</v>
       </c>
       <c r="B37" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>136274602</v>
       </c>
       <c r="B38" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>136274603</v>
       </c>
       <c r="B39" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>136274604</v>
       </c>
       <c r="B40" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>136274635</v>
       </c>
       <c r="B44" t="n">
-        <v>43409</v>
+        <v>43411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>136274620</v>
       </c>
       <c r="B45" t="n">
-        <v>56737</v>
+        <v>56739</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>136274598</v>
       </c>
       <c r="B46" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>136274628</v>
       </c>
       <c r="B47" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>136274668</v>
       </c>
       <c r="B48" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>136274606</v>
       </c>
       <c r="B49" t="n">
-        <v>98211</v>
+        <v>98216</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>136274590</v>
       </c>
       <c r="B50" t="n">
-        <v>102794</v>
+        <v>102799</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>136274592</v>
       </c>
       <c r="B51" t="n">
-        <v>102794</v>
+        <v>102799</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>136274621</v>
       </c>
       <c r="B52" t="n">
-        <v>102794</v>
+        <v>102799</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>136274633</v>
       </c>
       <c r="B53" t="n">
-        <v>102794</v>
+        <v>102799</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>136274638</v>
       </c>
       <c r="B54" t="n">
-        <v>102794</v>
+        <v>102799</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136274647</v>
       </c>
       <c r="B55" t="n">
-        <v>102794</v>
+        <v>102799</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136274664</v>
       </c>
       <c r="B56" t="n">
-        <v>102794</v>
+        <v>102799</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>136274667</v>
       </c>
       <c r="B57" t="n">
-        <v>102794</v>
+        <v>102799</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>136274670</v>
       </c>
       <c r="B58" t="n">
-        <v>102794</v>
+        <v>102799</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>136274565</v>
       </c>
       <c r="B59" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136274597</v>
       </c>
       <c r="B60" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/S 222-2023 artfynd.xlsx
+++ b/artfynd/S 222-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136274561</v>
       </c>
       <c r="B3" t="n">
-        <v>96654</v>
+        <v>96656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136274569</v>
       </c>
       <c r="B4" t="n">
-        <v>96654</v>
+        <v>96656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136274571</v>
       </c>
       <c r="B5" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136274587</v>
       </c>
       <c r="B6" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136274562</v>
       </c>
       <c r="B7" t="n">
-        <v>102477</v>
+        <v>102479</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136274573</v>
       </c>
       <c r="B8" t="n">
-        <v>102477</v>
+        <v>102479</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136274586</v>
       </c>
       <c r="B9" t="n">
-        <v>99157</v>
+        <v>99159</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>136274678</v>
       </c>
       <c r="B20" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136274680</v>
       </c>
       <c r="B21" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>136274674</v>
       </c>
       <c r="B24" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>136274683</v>
       </c>
       <c r="B25" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136274684</v>
       </c>
       <c r="B26" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>136274766</v>
       </c>
       <c r="B27" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>136274632</v>
       </c>
       <c r="B28" t="n">
-        <v>96459</v>
+        <v>96461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>136274598</v>
       </c>
       <c r="B46" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>136274628</v>
       </c>
       <c r="B47" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>136274668</v>
       </c>
       <c r="B48" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>136274606</v>
       </c>
       <c r="B49" t="n">
-        <v>98216</v>
+        <v>98218</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>136274590</v>
       </c>
       <c r="B50" t="n">
-        <v>102799</v>
+        <v>102801</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>136274592</v>
       </c>
       <c r="B51" t="n">
-        <v>102799</v>
+        <v>102801</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>136274621</v>
       </c>
       <c r="B52" t="n">
-        <v>102799</v>
+        <v>102801</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>136274633</v>
       </c>
       <c r="B53" t="n">
-        <v>102799</v>
+        <v>102801</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>136274638</v>
       </c>
       <c r="B54" t="n">
-        <v>102799</v>
+        <v>102801</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136274647</v>
       </c>
       <c r="B55" t="n">
-        <v>102799</v>
+        <v>102801</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136274664</v>
       </c>
       <c r="B56" t="n">
-        <v>102799</v>
+        <v>102801</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>136274667</v>
       </c>
       <c r="B57" t="n">
-        <v>102799</v>
+        <v>102801</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>136274670</v>
       </c>
       <c r="B58" t="n">
-        <v>102799</v>
+        <v>102801</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>136274565</v>
       </c>
       <c r="B59" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136274597</v>
       </c>
       <c r="B60" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
